--- a/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_FLEXICAR FUENLABRADA.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_FLEXICAR FUENLABRADA.xlsx
@@ -565,13 +565,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5053</v>
+        <v>7.672899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>10.3111</v>
+        <v>12.2607</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.8058</v>
+        <v>-4.587800000000001</v>
       </c>
       <c r="G2" t="n">
         <v>9.982900000000001</v>
@@ -610,13 +610,13 @@
         <v>6.3879</v>
       </c>
       <c r="S2" t="n">
-        <v>-6.1164</v>
+        <v>-2.9487</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.0982</v>
+        <v>-1.1487</v>
       </c>
       <c r="U2" t="n">
-        <v>-3.0182</v>
+        <v>-1.8001</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1234</v>
@@ -643,13 +643,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5089</v>
+        <v>4.914099999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5619</v>
+        <v>4.106800000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.05289999999999995</v>
+        <v>0.8070999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.5237</v>
@@ -688,13 +688,13 @@
         <v>5.7272</v>
       </c>
       <c r="S3" t="n">
-        <v>-4.9136</v>
+        <v>-2.5084</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.9061</v>
+        <v>-1.3609</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.0075</v>
+        <v>-1.1475</v>
       </c>
       <c r="V3" t="n">
         <v>0.3744</v>
@@ -721,13 +721,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.340800000000001</v>
+        <v>1.0949</v>
       </c>
       <c r="E4" t="n">
-        <v>1.429399999999999</v>
+        <v>0.801400000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08869999999999989</v>
+        <v>0.2935</v>
       </c>
       <c r="G4" t="n">
         <v>0.2216999999999998</v>
@@ -766,13 +766,13 @@
         <v>9.4717</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.259</v>
+        <v>-1.5048</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4818</v>
+        <v>-1.1097</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7773</v>
+        <v>-0.3951000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2652</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>V. ALVES BENITE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.9107</v>
+        <v>-0.8344</v>
       </c>
       <c r="E5" t="n">
-        <v>-6.4155</v>
+        <v>0.2758000000000003</v>
       </c>
       <c r="F5" t="n">
-        <v>4.5049</v>
+        <v>-1.1102</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5362</v>
+        <v>-3.6003</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7005</v>
+        <v>-2.9115</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2364</v>
+        <v>-0.6888000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7911</v>
+        <v>0.4899000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3227</v>
+        <v>-1.3713</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1138</v>
+        <v>1.8612</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2549</v>
+        <v>-4.0901</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3777999999999999</v>
+        <v>-1.5402</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8773</v>
+        <v>-2.55</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2202000000000002</v>
+        <v>0.4405000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-6.8285</v>
+        <v>-3.5244</v>
       </c>
       <c r="R5" t="n">
-        <v>6.6082</v>
+        <v>3.9649</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3857999999999999</v>
+        <v>-0.6568999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2503</v>
+        <v>-0.2314</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6361000000000001</v>
+        <v>-0.4254999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.6123</v>
+        <v>2.9823</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.1279</v>
+        <v>3.5417</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4845</v>
+        <v>-0.5595</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.944</v>
+        <v>-1.506</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2122</v>
+        <v>-1.8607</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2682</v>
+        <v>0.3547</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2127</v>
@@ -922,13 +922,13 @@
         <v>0.4405</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.07049999999999999</v>
+        <v>0.3675</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1922</v>
+        <v>0.1593</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1217</v>
+        <v>0.2082</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. ALVES BENITE</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9649</v>
+        <v>-1.804</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2582</v>
+        <v>-6.2873</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7067000000000001</v>
+        <v>4.4836</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.6003</v>
+        <v>0.5362</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.9115</v>
+        <v>-1.7005</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6888000000000001</v>
+        <v>2.2364</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4899000000000001</v>
+        <v>1.7911</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3713</v>
+        <v>-1.3227</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8612</v>
+        <v>3.1138</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.0901</v>
+        <v>-1.2549</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5402</v>
+        <v>-0.3777999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.55</v>
+        <v>-0.8773</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4405000000000001</v>
+        <v>-0.2202000000000002</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.5244</v>
+        <v>-6.8285</v>
       </c>
       <c r="R7" t="n">
-        <v>3.9649</v>
+        <v>6.6082</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7874</v>
+        <v>0.4925</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.7654</v>
+        <v>-0.1223000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.02200000000000002</v>
+        <v>0.6148</v>
       </c>
       <c r="V7" t="n">
-        <v>2.9823</v>
+        <v>-2.6123</v>
       </c>
       <c r="W7" t="n">
-        <v>3.5417</v>
+        <v>-1.1279</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5595</v>
+        <v>-1.4845</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0677</v>
+        <v>-2.0119</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8074</v>
+        <v>-1.9245</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2603</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2228</v>
@@ -1078,13 +1078,13 @@
         <v>0.4405</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.369</v>
+        <v>-0.3133</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0124</v>
+        <v>-0.1047</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3815</v>
+        <v>-0.2085</v>
       </c>
       <c r="V8" t="n">
         <v>0.185</v>
@@ -1111,13 +1111,13 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4067</v>
+        <v>-2.1614</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3133000000000001</v>
+        <v>-0.4835000000000002</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0935</v>
+        <v>-1.6777</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4314</v>
@@ -1156,13 +1156,13 @@
         <v>0.8811</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5957</v>
+        <v>-0.3503</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01250000000000007</v>
+        <v>-0.1579</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6082</v>
+        <v>-0.1925</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2608</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>M. DIAZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.490600000000001</v>
+        <v>-5.2667</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2897</v>
+        <v>-6.1254</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.201</v>
+        <v>0.8586</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3474</v>
+        <v>-6.4509</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1989</v>
+        <v>-1.4571</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.5462</v>
+        <v>-4.9937</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5214</v>
+        <v>-0.4916</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6622</v>
+        <v>0.6086</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1409</v>
+        <v>-1.1003</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.8687</v>
+        <v>-5.9592</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4635000000000001</v>
+        <v>-2.0657</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.4053</v>
+        <v>-3.8934</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4406</v>
+        <v>3.0838</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.6258</v>
+        <v>-4.4054</v>
       </c>
       <c r="R10" t="n">
-        <v>5.0662</v>
+        <v>7.4892</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1041</v>
+        <v>-2.3878</v>
       </c>
       <c r="T10" t="n">
-        <v>1.568</v>
+        <v>-1.2283</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5361</v>
+        <v>-1.1596</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.688</v>
+        <v>0.4881</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7534000000000001</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.9347</v>
+        <v>0.4881</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. LIMA BRITO</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5422</v>
+        <v>-5.3905</v>
       </c>
       <c r="E11" t="n">
-        <v>1.456</v>
+        <v>-3.5675</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.9982</v>
+        <v>-1.8232</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.0997</v>
+        <v>-3.3474</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8251999999999999</v>
+        <v>1.1989</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2746</v>
+        <v>-4.5462</v>
       </c>
       <c r="J11" t="n">
-        <v>1.445</v>
+        <v>1.5214</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9092999999999999</v>
+        <v>1.6622</v>
       </c>
       <c r="L11" t="n">
-        <v>2.3544</v>
+        <v>-0.1409</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.5447</v>
+        <v>-4.8687</v>
       </c>
       <c r="N11" t="n">
-        <v>0.08410000000000012</v>
+        <v>-0.4635000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.6288</v>
+        <v>-4.4053</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2202000000000002</v>
+        <v>0.4406</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.4055</v>
+        <v>-4.6258</v>
       </c>
       <c r="R11" t="n">
-        <v>4.1851</v>
+        <v>5.0662</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4608</v>
+        <v>0.2042</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3021</v>
+        <v>0.2901</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.8415</v>
+        <v>-0.08600000000000002</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6829</v>
+        <v>-2.688</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1144</v>
+        <v>-0.7534000000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7973</v>
+        <v>-1.9347</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. DIAZ</t>
+          <t>A. LIMA BRITO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.262499999999999</v>
+        <v>-6.3264</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.4796</v>
+        <v>-1.3979</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2169000000000001</v>
+        <v>-4.9285</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.4509</v>
+        <v>-3.0997</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4571</v>
+        <v>-0.8251999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.9937</v>
+        <v>-2.2746</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4916</v>
+        <v>1.445</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6086</v>
+        <v>-0.9092999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1003</v>
+        <v>2.3544</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.9592</v>
+        <v>-4.5447</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0657</v>
+        <v>0.08410000000000012</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.8934</v>
+        <v>-4.6288</v>
       </c>
       <c r="P12" t="n">
-        <v>3.0838</v>
+        <v>-0.2202000000000002</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.4054</v>
+        <v>-4.4055</v>
       </c>
       <c r="R12" t="n">
-        <v>7.4892</v>
+        <v>4.1851</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.3836</v>
+        <v>-1.3236</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.5825</v>
+        <v>0.4481000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.8011</v>
+        <v>-1.7717</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4881</v>
+        <v>-1.6829</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1144</v>
       </c>
       <c r="X12" t="n">
-        <v>0.4881</v>
+        <v>-2.7973</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.4238</v>
+        <v>-11.3131</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.6175</v>
+        <v>-8.831199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.8064</v>
+        <v>-2.4818</v>
       </c>
       <c r="G13" t="n">
         <v>-4.3535</v>
@@ -1468,13 +1468,13 @@
         <v>6.6082</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7569000000000001</v>
+        <v>-1.6462</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7306999999999999</v>
+        <v>-0.483</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4877</v>
+        <v>-1.1631</v>
       </c>
       <c r="V13" t="n">
         <v>-6.4148</v>
@@ -1501,13 +1501,13 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.6581</v>
+        <v>-22.9325</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.635</v>
+        <v>-13.0333</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.0235</v>
+        <v>-9.899100000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-11.4542</v>
@@ -1522,16 +1522,16 @@
         <v>21.3576</v>
       </c>
       <c r="K14" t="n">
-        <v>3.777100000000001</v>
+        <v>3.7771</v>
       </c>
       <c r="L14" t="n">
         <v>17.5803</v>
       </c>
       <c r="M14" t="n">
-        <v>-32.81139999999999</v>
+        <v>-32.8114</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.5072</v>
+        <v>-6.507199999999999</v>
       </c>
       <c r="O14" t="n">
         <v>-26.3046</v>
@@ -1546,13 +1546,13 @@
         <v>57.27069999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-17.3014</v>
+        <v>-12.5758</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.6508</v>
+        <v>-5.049399999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-10.6511</v>
+        <v>-7.526600000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-11.0176</v>
